--- a/R099N.xlsx
+++ b/R099N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
   <si>
     <t/>
   </si>
@@ -32,6 +32,78 @@
   </si>
   <si>
     <t>RT,(E-7H)</t>
+  </si>
+  <si>
+    <t>20142876</t>
+  </si>
+  <si>
+    <t>DLEZZ SWS.ROL STR 72</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>787</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20142877</t>
+  </si>
+  <si>
+    <t>DALEZZ CUSTARD 100G</t>
+  </si>
+  <si>
+    <t>788</t>
+  </si>
+  <si>
+    <t>20142878</t>
+  </si>
+  <si>
+    <t>DALEZZ MUFFIN 84G</t>
+  </si>
+  <si>
+    <t>789</t>
+  </si>
+  <si>
+    <t>20143040</t>
+  </si>
+  <si>
+    <t>OBLB SQR ORI FLV CKE</t>
+  </si>
+  <si>
+    <t>790</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20143041</t>
+  </si>
+  <si>
+    <t>OBLB TRNGLE STRW CKE</t>
+  </si>
+  <si>
+    <t>791</t>
+  </si>
+  <si>
+    <t>20143042</t>
+  </si>
+  <si>
+    <t>OBLB TRGLE CHO CAKE</t>
+  </si>
+  <si>
+    <t>792</t>
+  </si>
+  <si>
+    <t>20143043</t>
+  </si>
+  <si>
+    <t>OBLB TRGLE CHSE CAKE</t>
+  </si>
+  <si>
+    <t>793</t>
   </si>
 </sst>
 </file>
@@ -424,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -475,6 +547,146 @@
         <v>6</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
